--- a/data/availability/projects/al-marasem-developments/marville.xlsx
+++ b/data/availability/projects/al-marasem-developments/marville.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -859,7 +859,6 @@
       <c r="G2" t="n">
         <v>96</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -870,7 +869,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -931,7 +930,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -992,7 +991,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1053,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
